--- a/business_forms/035_spa_franchise_inquiry_registration_form--business_forms.xlsx
+++ b/business_forms/035_spa_franchise_inquiry_registration_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'address',_'value':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Address', 'value': 'address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'location',_'value':_'location'}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Location', 'value': 'location'}</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'business_name',_'value':_'business_name'}</t>
+          <t>business_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Business Name', 'value': 'business_name'}</t>
+          <t>Business Name</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'business_type',_'value':_'business_type'}</t>
+          <t>business_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Business Type', 'value': 'business_type'}</t>
+          <t>Business Type</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'spa',_'value':_'spa'}</t>
+          <t>spa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Spa', 'value': 'spa'}</t>
+          <t>Spa</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'massage',_'value':_'massage'}</t>
+          <t>massage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Massage', 'value': 'massage'}</t>
+          <t>Massage</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'beauty',_'value':_'beauty'}</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Beauty', 'value': 'beauty'}</t>
+          <t>Beauty</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'usd',_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'USD', 'value': 'usd'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'eur',_'value':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'EUR', 'value': 'eur'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'gbp',_'value':_'gbp'}</t>
+          <t>gbp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'GBP', 'value': 'gbp'}</t>
+          <t>GBP</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'brand_a',_'value':_'brand_a'}</t>
+          <t>brand_a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Brand A', 'value': 'brand_a'}</t>
+          <t>Brand A</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'brand_b',_'value':_'brand_b'}</t>
+          <t>brand_b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Brand B', 'value': 'brand_b'}</t>
+          <t>Brand B</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'brand_c',_'value':_'brand_c'}</t>
+          <t>brand_c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Brand C', 'value': 'brand_c'}</t>
+          <t>Brand C</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'new_lead',_'value':_'new_lead'}</t>
+          <t>new_lead</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'New Lead', 'value': 'new_lead'}</t>
+          <t>New Lead</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'qualified_lead',_'value':_'qualified_lead'}</t>
+          <t>qualified_lead</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Qualified Lead', 'value': 'qualified_lead'}</t>
+          <t>Qualified Lead</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'disqualified_lead',_'value':_'disqualified_lead'}</t>
+          <t>disqualified_lead</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Disqualified Lead', 'value': 'disqualified_lead'}</t>
+          <t>Disqualified Lead</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'mail',_'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Mail', 'value': 'mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
